--- a/exports/UNIONBANK_full_report.xlsx
+++ b/exports/UNIONBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.67</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>38</v>
+        <v>36.03</v>
       </c>
       <c r="I2" t="n">
         <v>37.51125193043001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.16</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>6.31</v>
+        <v>9.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>4.95</v>
       </c>
       <c r="O2" t="n">
         <v>1.79</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>10.26</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44586.55208333334</v>
+        <v>44588.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>36.74</v>
+        <v>39.09</v>
       </c>
       <c r="I3" t="n">
         <v>38.86616892268642</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.97</v>
+        <v>-8.49</v>
       </c>
       <c r="L3" t="n">
-        <v>4.58</v>
+        <v>8.85</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>-4.95</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.85</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>40.07</v>
+        <v>38.19</v>
       </c>
       <c r="I4" t="n">
         <v>38.37990374032799</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>2.51</v>
+        <v>-2.3</v>
       </c>
       <c r="L4" t="n">
         <v>7.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17</v>
+        <v>3.39</v>
       </c>
       <c r="N4" t="n">
-        <v>4.21</v>
+        <v>8.44</v>
       </c>
       <c r="O4" t="n">
         <v>9.960000000000001</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>32.88</v>
+        <v>34.25</v>
       </c>
       <c r="I5" t="n">
         <v>33.793168360897</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9</v>
+        <v>10.32</v>
       </c>
       <c r="L5" t="n">
         <v>2.7</v>
@@ -726,7 +785,7 @@
         <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>5.12</v>
+        <v>7.45</v>
       </c>
       <c r="O5" t="n">
         <v>-8.44</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>35.94</v>
+        <v>34.85</v>
       </c>
       <c r="I6" t="n">
         <v>35.03809478715618</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>4.93</v>
+        <v>1.75</v>
       </c>
       <c r="L6" t="n">
         <v>4.26</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.82</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44694.55208333334</v>
+        <v>44697.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>30.54</v>
+        <v>31.1</v>
       </c>
       <c r="I7" t="n">
         <v>31.08228727636759</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>12.37</v>
+        <v>10.76</v>
       </c>
       <c r="L7" t="n">
         <v>4.33</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>31.62</v>
+        <v>30.72</v>
       </c>
       <c r="I8" t="n">
         <v>31.41324456814549</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>1.67</v>
+        <v>-1.22</v>
       </c>
       <c r="L8" t="n">
         <v>6.66</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.83</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44750.38541666666</v>
+        <v>44750.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>30.34</v>
+        <v>30.39</v>
       </c>
       <c r="I9" t="n">
         <v>30.38955116012247</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="L9" t="n">
         <v>2.93</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.25</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.38541666666</v>
+        <v>44827.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>38.33</v>
+        <v>38.1</v>
       </c>
       <c r="I10" t="n">
         <v>38.28087695334781</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76.83333333333333</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>26.13</v>
+        <v>25.37</v>
       </c>
       <c r="L10" t="n">
         <v>0.76</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>37.86</v>
+        <v>39.83</v>
       </c>
       <c r="I11" t="n">
         <v>39.26275385014187</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.63</v>
+        <v>-4.54</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>4.93</v>
       </c>
       <c r="M11" t="n">
         <v>2.92</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.92</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44911.55208333334</v>
+        <v>44914.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>76.84999999999999</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>76.01020951376181</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K12" t="n">
-        <v>92.95</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.24</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.93</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.38541666666</v>
+        <v>44921.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>66.7</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>72.61964658404533</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>12.19</v>
+        <v>4.21</v>
       </c>
       <c r="L13" t="n">
         <v>3.33</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>21.91</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>70.18000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="I14" t="n">
         <v>68.63806765157767</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>30</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.55</v>
+        <v>-10.58</v>
       </c>
       <c r="L14" t="n">
-        <v>8.77</v>
+        <v>11.23</v>
       </c>
       <c r="M14" t="n">
         <v>0.38</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>59.28</v>
+        <v>64.08</v>
       </c>
       <c r="I15" t="n">
         <v>63.01986932901507</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>8.880000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="L15" t="n">
         <v>9.9</v>
@@ -1296,7 +1475,7 @@
         <v>6.03</v>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>9.67</v>
       </c>
       <c r="O15" t="n">
         <v>-4.27</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>10.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>61.63</v>
+        <v>59</v>
       </c>
       <c r="I16" t="n">
         <v>61.15146273030689</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.82</v>
+        <v>-7.93</v>
       </c>
       <c r="L16" t="n">
-        <v>6.24</v>
+        <v>8.82</v>
       </c>
       <c r="M16" t="n">
         <v>1.26</v>
       </c>
       <c r="N16" t="n">
-        <v>2.24</v>
+        <v>4.19</v>
       </c>
       <c r="O16" t="n">
         <v>9.67</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>56</v>
+        <v>58.91</v>
       </c>
       <c r="I17" t="n">
         <v>58.7473763213822</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>5.08</v>
+        <v>0.15</v>
       </c>
       <c r="L17" t="n">
         <v>5.02</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.81</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>66.09</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>65.85070437081772</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>12.19</v>
+        <v>10.75</v>
       </c>
       <c r="L18" t="n">
         <v>4.94</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.23</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>63.51</v>
+        <v>64.73</v>
       </c>
       <c r="I19" t="n">
         <v>64.5315053290129</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>2.65</v>
+        <v>0.78</v>
       </c>
       <c r="L19" t="n">
         <v>2.82</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.33</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45092.38541666666</v>
+        <v>45092.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>63.09</v>
+        <v>62.57</v>
       </c>
       <c r="I20" t="n">
         <v>62.58259645312528</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.53</v>
+        <v>-3.34</v>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>3.55</v>
       </c>
       <c r="M20" t="n">
         <v>0.08</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.23</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45107.38541666666</v>
+        <v>45107.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>63.37</v>
+        <v>64.59</v>
       </c>
       <c r="I21" t="n">
         <v>63.57494559840842</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.28</v>
+        <v>-3.23</v>
       </c>
       <c r="L21" t="n">
         <v>3.61</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>83.23999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="I22" t="n">
         <v>79.91177231186576</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>59</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>28.87</v>
+        <v>21.01</v>
       </c>
       <c r="L22" t="n">
         <v>1.97</v>
@@ -1695,7 +1958,7 @@
         <v>2.76</v>
       </c>
       <c r="N22" t="n">
-        <v>2.76</v>
+        <v>6.55</v>
       </c>
       <c r="O22" t="n">
         <v>2.46</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45182.55208333334</v>
+        <v>45183.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>82.06999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="I23" t="n">
         <v>82.39930538467252</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>-5</v>
+        <v>-6.81</v>
       </c>
       <c r="L23" t="n">
-        <v>7.69</v>
+        <v>8.18</v>
       </c>
       <c r="M23" t="n">
         <v>1.26</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="O23" t="n">
         <v>-6.55</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.78</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>95.31999999999999</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>92.90769260358425</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>14.18</v>
+        <v>9.56</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0.25</v>
+        <v>2.52</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>5.72</v>
       </c>
       <c r="O24" t="n">
         <v>4.18</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.62</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45230.55208333334</v>
+        <v>45231.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>91.69</v>
+        <v>93.38</v>
       </c>
       <c r="I25" t="n">
         <v>93.06856615942787</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.25</v>
+        <v>-2.1</v>
       </c>
       <c r="L25" t="n">
         <v>5.81</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45252.38541666666</v>
+        <v>45252.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>97.38</v>
+        <v>96.53</v>
       </c>
       <c r="I26" t="n">
         <v>96.8412644749848</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>4.28</v>
+        <v>3.37</v>
       </c>
       <c r="L26" t="n">
         <v>2.46</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.61</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>98.65000000000001</v>
+        <v>103.95</v>
       </c>
       <c r="I27" t="n">
         <v>102.6525362995156</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.2</v>
+        <v>-7.69</v>
       </c>
       <c r="L27" t="n">
-        <v>5.41</v>
+        <v>8.27</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>1.97</v>
+        <v>5.23</v>
       </c>
       <c r="O27" t="n">
         <v>-3.07</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.62</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>111.05</v>
+        <v>106.3</v>
       </c>
       <c r="I28" t="n">
         <v>106.7614423900101</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>6.83</v>
+        <v>2.26</v>
       </c>
       <c r="L28" t="n">
         <v>1.98</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>113.59</v>
+        <v>120.4</v>
       </c>
       <c r="I29" t="n">
         <v>114.9943165143568</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.86</v>
+        <v>-13.26</v>
       </c>
       <c r="L29" t="n">
-        <v>7.83</v>
+        <v>13.92</v>
       </c>
       <c r="M29" t="n">
         <v>0.87</v>
       </c>
       <c r="N29" t="n">
-        <v>1.92</v>
+        <v>5.58</v>
       </c>
       <c r="O29" t="n">
         <v>-4.83</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45334.55208333334</v>
+        <v>45335.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>127.3</v>
+        <v>124.39</v>
       </c>
       <c r="I30" t="n">
         <v>126.4925441758457</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K30" t="n">
-        <v>5.73</v>
+        <v>3.31</v>
       </c>
       <c r="L30" t="n">
         <v>5.78</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>16.6</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>136.46</v>
+        <v>142.29</v>
       </c>
       <c r="I31" t="n">
         <v>138.7847475694216</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.699999999999999</v>
+        <v>-14.39</v>
       </c>
       <c r="L31" t="n">
-        <v>11.18</v>
+        <v>15.79</v>
       </c>
       <c r="M31" t="n">
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>4.87</v>
+        <v>6.3</v>
       </c>
       <c r="O31" t="n">
         <v>-2.14</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.64</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>138.02</v>
+        <v>130.45</v>
       </c>
       <c r="I32" t="n">
         <v>132.4732900022697</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>-3</v>
+        <v>-8.32</v>
       </c>
       <c r="L32" t="n">
-        <v>4.76</v>
+        <v>9.35</v>
       </c>
       <c r="M32" t="n">
         <v>0.03</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>5.86</v>
       </c>
       <c r="O32" t="n">
         <v>6.3</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.84</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>143.42</v>
+        <v>143.75</v>
       </c>
       <c r="I33" t="n">
         <v>143.6328735865598</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.94</v>
+        <v>-10.2</v>
       </c>
       <c r="L33" t="n">
-        <v>10.23</v>
+        <v>10.48</v>
       </c>
       <c r="M33" t="n">
         <v>1.67</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.48</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45391.55208333334</v>
+        <v>45392.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>139.33</v>
+        <v>137.92</v>
       </c>
       <c r="I34" t="n">
         <v>139.0494974311022</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.07</v>
+        <v>-4.06</v>
       </c>
       <c r="L34" t="n">
-        <v>3.67</v>
+        <v>4.42</v>
       </c>
       <c r="M34" t="n">
         <v>1.21</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.27</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45404.38541666666</v>
+        <v>45404.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>134.39</v>
+        <v>138.25</v>
       </c>
       <c r="I35" t="n">
         <v>137.3199341946904</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>2.56</v>
+        <v>-0.24</v>
       </c>
       <c r="L35" t="n">
         <v>2.01</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>139.84</v>
+        <v>134.11</v>
       </c>
       <c r="I36" t="n">
         <v>134.8042751063533</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>1.15</v>
+        <v>-2.99</v>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>3.91</v>
       </c>
       <c r="M36" t="n">
         <v>0.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>7.02</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>130.91</v>
+        <v>136.41</v>
       </c>
       <c r="I37" t="n">
         <v>134.6024348335805</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>2.39</v>
+        <v>-1.72</v>
       </c>
       <c r="L37" t="n">
         <v>5.5</v>
@@ -2550,7 +2993,7 @@
         <v>1.24</v>
       </c>
       <c r="N37" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="O37" t="n">
         <v>-2.65</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>9.35</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>156.38</v>
+        <v>131.76</v>
       </c>
       <c r="I38" t="n">
         <v>143.1002709425039</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>14.64</v>
+        <v>-3.41</v>
       </c>
       <c r="L38" t="n">
-        <v>3.64</v>
+        <v>8.81</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>18.05</v>
       </c>
       <c r="O38" t="n">
         <v>3.95</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>23.29</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45481.55208333334</v>
+        <v>45482.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>121.9</v>
+        <v>127.94</v>
       </c>
       <c r="I39" t="n">
         <v>127.4972195919787</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>7.48</v>
+        <v>2.9</v>
       </c>
       <c r="L39" t="n">
         <v>18.58</v>
@@ -2664,7 +3131,7 @@
         <v>2.58</v>
       </c>
       <c r="N39" t="n">
-        <v>2.87</v>
+        <v>4.89</v>
       </c>
       <c r="O39" t="n">
         <v>-18.05</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.34</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>125.1</v>
+        <v>119.02</v>
       </c>
       <c r="I40" t="n">
         <v>121.8626129087598</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.22</v>
+        <v>-6.97</v>
       </c>
       <c r="L40" t="n">
-        <v>5.2</v>
+        <v>8.07</v>
       </c>
       <c r="M40" t="n">
-        <v>0.72</v>
+        <v>2.74</v>
       </c>
       <c r="N40" t="n">
-        <v>2.15</v>
+        <v>5.77</v>
       </c>
       <c r="O40" t="n">
         <v>4.89</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.88</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>113.11</v>
+        <v>116.92</v>
       </c>
       <c r="I41" t="n">
         <v>116.4978985021871</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>4.97</v>
+        <v>1.76</v>
       </c>
       <c r="L41" t="n">
         <v>2.5</v>
@@ -2778,7 +3269,7 @@
         <v>2.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.43</v>
+        <v>4.23</v>
       </c>
       <c r="O41" t="n">
         <v>-5.77</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.34</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>113.92</v>
+        <v>111.24</v>
       </c>
       <c r="I42" t="n">
         <v>113.5141306105338</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.57</v>
+        <v>-4.86</v>
       </c>
       <c r="L42" t="n">
-        <v>3.58</v>
+        <v>5.9</v>
       </c>
       <c r="M42" t="n">
         <v>2.21</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.6</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>115.46</v>
+        <v>117.01</v>
       </c>
       <c r="I43" t="n">
         <v>116.7844693072369</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.79</v>
+        <v>-5.19</v>
       </c>
       <c r="L43" t="n">
         <v>7.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>114.54</v>
+        <v>111.96</v>
       </c>
       <c r="I44" t="n">
         <v>113.3233385949294</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.11</v>
+        <v>-4.32</v>
       </c>
       <c r="L44" t="n">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="M44" t="n">
-        <v>0.38</v>
+        <v>1.57</v>
       </c>
       <c r="N44" t="n">
         <v>3.78</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>107.38</v>
+        <v>108.98</v>
       </c>
       <c r="I45" t="n">
         <v>108.6029145513965</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>4.09</v>
+        <v>2.66</v>
       </c>
       <c r="L45" t="n">
         <v>1.72</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.44</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45644.38541666666</v>
+        <v>45644.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>116.49</v>
+        <v>115.31</v>
       </c>
       <c r="I46" t="n">
         <v>115.7532367311702</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
-        <v>6.89</v>
+        <v>5.81</v>
       </c>
       <c r="L46" t="n">
         <v>3.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>5.57</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>114.29</v>
+        <v>117.31</v>
       </c>
       <c r="I47" t="n">
         <v>116.8116047139386</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>0.88</v>
+        <v>-1.73</v>
       </c>
       <c r="L47" t="n">
-        <v>1.13</v>
+        <v>3.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0.32</v>
+        <v>0.78</v>
       </c>
       <c r="N47" t="n">
         <v>2.71</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.23</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>116.5</v>
+        <v>108.34</v>
       </c>
       <c r="I48" t="n">
         <v>109.1695990237056</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-7.65</v>
       </c>
       <c r="L48" t="n">
-        <v>2.11</v>
+        <v>8.06</v>
       </c>
       <c r="M48" t="n">
-        <v>-0</v>
+        <v>0.15</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="O48" t="n">
         <v>1.93</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.24</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>102.03</v>
+        <v>105.21</v>
       </c>
       <c r="I49" t="n">
         <v>103.720171052454</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>5.82</v>
+        <v>2.89</v>
       </c>
       <c r="L49" t="n">
         <v>7.37</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.56</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>107.71</v>
+        <v>104.14</v>
       </c>
       <c r="I50" t="n">
         <v>105.3986976369464</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K50" t="n">
-        <v>2.38</v>
+        <v>-1.02</v>
       </c>
       <c r="L50" t="n">
         <v>6.71</v>
@@ -3291,7 +3890,7 @@
         <v>1.14</v>
       </c>
       <c r="N50" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="O50" t="n">
         <v>2.49</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>107.76</v>
+        <v>109.3</v>
       </c>
       <c r="I51" t="n">
         <v>109.2228261347668</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.48</v>
+        <v>-4.95</v>
       </c>
       <c r="L51" t="n">
-        <v>4.62</v>
+        <v>6.45</v>
       </c>
       <c r="M51" t="n">
         <v>0.61</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751.38541666666</v>
+        <v>45751.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>116.35</v>
+        <v>114.99</v>
       </c>
       <c r="I52" t="n">
         <v>115.2110801742855</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>6.45</v>
+        <v>5.21</v>
       </c>
       <c r="L52" t="n">
         <v>7.51</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>118.84</v>
+        <v>121.31</v>
       </c>
       <c r="I53" t="n">
         <v>119.8218375529459</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.35</v>
+        <v>-5.5</v>
       </c>
       <c r="L53" t="n">
-        <v>4.45</v>
+        <v>6.13</v>
       </c>
       <c r="M53" t="n">
         <v>2.79</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>114.05</v>
+        <v>111.24</v>
       </c>
       <c r="I54" t="n">
         <v>113.2777606237532</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.98</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>6.29</v>
+        <v>8.85</v>
       </c>
       <c r="M54" t="n">
         <v>0.87</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>7.95</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>115.46</v>
+        <v>119.9</v>
       </c>
       <c r="I55" t="n">
         <v>118.8346548673389</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.79</v>
+        <v>-7.78</v>
       </c>
       <c r="L55" t="n">
-        <v>4.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>1.27</v>
+        <v>2.52</v>
       </c>
       <c r="N55" t="n">
         <v>6.87</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>138.21</v>
+        <v>136.36</v>
       </c>
       <c r="I56" t="n">
         <v>137.3813408524716</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>15.27</v>
+        <v>13.73</v>
       </c>
       <c r="L56" t="n">
         <v>1.35</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.82</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>139.04</v>
+        <v>141.96</v>
       </c>
       <c r="I57" t="n">
         <v>139.2512905339425</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.97</v>
+        <v>-4.11</v>
       </c>
       <c r="L57" t="n">
-        <v>2.51</v>
+        <v>4.66</v>
       </c>
       <c r="M57" t="n">
         <v>1.23</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.68</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>141.4</v>
+        <v>136.08</v>
       </c>
       <c r="I58" t="n">
         <v>136.8109971739733</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.39</v>
+        <v>-4.14</v>
       </c>
       <c r="L58" t="n">
-        <v>2.3</v>
+        <v>6.33</v>
       </c>
       <c r="M58" t="n">
-        <v>0.29</v>
+        <v>1.76</v>
       </c>
       <c r="N58" t="n">
-        <v>1.15</v>
+        <v>3.85</v>
       </c>
       <c r="O58" t="n">
         <v>1.29</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45880.38541666666</v>
+        <v>45880.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>129.34</v>
+        <v>130.89</v>
       </c>
       <c r="I59" t="n">
         <v>130.2787813479438</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>4.95</v>
+        <v>3.81</v>
       </c>
       <c r="L59" t="n">
         <v>3.28</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.28</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>129.14</v>
+        <v>125.83</v>
       </c>
       <c r="I60" t="n">
         <v>128.2106017331393</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.34</v>
+        <v>-3.87</v>
       </c>
       <c r="L60" t="n">
-        <v>1.43</v>
+        <v>4.09</v>
       </c>
       <c r="M60" t="n">
         <v>0.37</v>
       </c>
       <c r="N60" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="O60" t="n">
         <v>2.95</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.91</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>123.94</v>
+        <v>128.14</v>
       </c>
       <c r="I61" t="n">
         <v>127.6901583429543</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>1.5</v>
+        <v>-1.84</v>
       </c>
       <c r="L61" t="n">
         <v>2.67</v>
@@ -3918,7 +4649,7 @@
         <v>0.99</v>
       </c>
       <c r="N61" t="n">
-        <v>2.65</v>
+        <v>3.82</v>
       </c>
       <c r="O61" t="n">
         <v>-2.32</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.88</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>148.99</v>
+        <v>143.96</v>
       </c>
       <c r="I62" t="n">
         <v>145.331661735699</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>86.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K62" t="n">
-        <v>16.27</v>
+        <v>12.35</v>
       </c>
       <c r="L62" t="n">
         <v>3.07</v>
@@ -3975,7 +4718,7 @@
         <v>0.57</v>
       </c>
       <c r="N62" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="O62" t="n">
         <v>3.82</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>7.67</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>146.67</v>
+        <v>150.48</v>
       </c>
       <c r="I63" t="n">
         <v>149.8011262388086</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.88</v>
+        <v>-4.53</v>
       </c>
       <c r="L63" t="n">
         <v>4.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="N63" t="n">
         <v>1.94</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>164.52</v>
+        <v>162.51</v>
       </c>
       <c r="I64" t="n">
         <v>163.6250087288361</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K64" t="n">
-        <v>9.33</v>
+        <v>7.99</v>
       </c>
       <c r="L64" t="n">
         <v>2.29</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>10.34</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>178.63</v>
+        <v>183.14</v>
       </c>
       <c r="I65" t="n">
         <v>179.3115436366785</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.92</v>
+        <v>-12.69</v>
       </c>
       <c r="L65" t="n">
-        <v>9.970000000000001</v>
+        <v>13.56</v>
       </c>
       <c r="M65" t="n">
         <v>4.51</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.47</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46085.38541666666</v>
+        <v>46085.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>186.76</v>
+        <v>185.43</v>
       </c>
       <c r="I66" t="n">
         <v>185.8812200324631</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="L66" t="n">
         <v>3.55</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>7.39</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>167.36</v>
+        <v>179.51</v>
       </c>
       <c r="I67" t="n">
         <v>176.7647867895014</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>9.74</v>
+        <v>3.19</v>
       </c>
       <c r="L67" t="n">
         <v>2.36</v>
       </c>
       <c r="M67" t="n">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>7.95</v>
       </c>
       <c r="O67" t="n">
         <v>-3.97</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>11.51</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46135.38541666666</v>
+        <v>46135.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>178.31</v>
+        <v>174.35</v>
       </c>
       <c r="I68" t="n">
         <v>177.3365017521512</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.67</v>
+        <v>-2.87</v>
       </c>
       <c r="L68" t="n">
-        <v>3.25</v>
+        <v>4.06</v>
       </c>
       <c r="M68" t="n">
         <v>4.02</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.67</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>160.5</v>
+        <v>164.6</v>
       </c>
       <c r="I69" t="n">
         <v>161.3519494358578</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K69" t="n">
-        <v>7.94</v>
+        <v>5.59</v>
       </c>
       <c r="L69" t="n">
         <v>2.37</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.5</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>169.39</v>
+        <v>163.23</v>
       </c>
       <c r="I70" t="n">
         <v>163.837093280969</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>2.91</v>
+        <v>-0.83</v>
       </c>
       <c r="L70" t="n">
         <v>5.52</v>
@@ -4431,7 +5270,7 @@
         <v>1.34</v>
       </c>
       <c r="N70" t="n">
-        <v>2.9</v>
+        <v>3.72</v>
       </c>
       <c r="O70" t="n">
         <v>5.19</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.58</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46213.38541666666</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>163.01</v>
+        <v>164.69</v>
       </c>
       <c r="I71" t="n">
         <v>164.1099011322817</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>0.13</v>
+        <v>-0.89</v>
       </c>
       <c r="L71" t="n">
         <v>3.41</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.61</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46274.55208333334</v>
+        <v>46275.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>182.67</v>
+        <v>179.4</v>
       </c>
       <c r="I72" t="n">
         <v>181.2665775658871</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K72" t="n">
-        <v>10.92</v>
+        <v>8.93</v>
       </c>
       <c r="L72" t="n">
         <v>1.74</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.02</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46311.55208333334</v>
+        <v>46314.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>172.67</v>
+        <v>179.63</v>
       </c>
       <c r="I73" t="n">
         <v>174.9401460475715</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K73" t="n">
-        <v>3.75</v>
+        <v>-0.13</v>
       </c>
       <c r="L73" t="n">
         <v>2.81</v>
@@ -4602,7 +5477,7 @@
         <v>1.36</v>
       </c>
       <c r="N73" t="n">
-        <v>3.47</v>
+        <v>4.94</v>
       </c>
       <c r="O73" t="n">
         <v>-2.18</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4662,6 +5549,12 @@
       <c r="Q74" t="n">
         <v>12</v>
       </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6764,7 +7657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="6">
@@ -6774,7 +7667,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="7">
@@ -6784,7 +7677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -6794,7 +7687,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6804,7 +7697,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6814,7 +7707,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="11">
@@ -6824,7 +7717,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -6834,7 +7727,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6844,7 +7737,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.59999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="14">
@@ -6854,7 +7747,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.17</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
@@ -6864,7 +7757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.01</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="16">
@@ -6874,7 +7767,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.33</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="17">
@@ -6884,7 +7777,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92.95</v>
+        <v>90.70999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6894,7 +7787,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.7</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="19">
@@ -6904,7 +7797,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.54</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="20">
@@ -6914,7 +7807,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.62</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="21">
@@ -6934,7 +7827,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -6944,7 +7837,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6954,7 +7847,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -6974,7 +7867,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.92</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="27">
@@ -6994,7 +7887,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
